--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487528_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487528_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2708</v>
+        <v>5.4979</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2033</v>
+        <v>6.4839</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9325</v>
+        <v>-0.9859</v>
       </c>
       <c r="G2" t="n">
         <v>2.0972</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8126</v>
+        <v>-0.5855</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2506</v>
+        <v>0.03</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6155</v>
       </c>
       <c r="V2" t="n">
         <v>3.007</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0596</v>
+        <v>2.9179</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2333</v>
+        <v>2.0006</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8263</v>
+        <v>0.9173</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2775</v>
+        <v>2.1467</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5104</v>
+        <v>-2.0565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2328</v>
+        <v>4.2032</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6475</v>
+        <v>3.3998</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2416</v>
+        <v>-1.5857</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8891</v>
+        <v>4.9855</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.925</v>
+        <v>-1.2532</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2687</v>
+        <v>-0.4708</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6563</v>
+        <v>-0.7823</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9254</v>
+        <v>-0.2103</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5858</v>
+        <v>-0.2241</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3397</v>
+        <v>0.0138</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2574</v>
+        <v>-0.5853</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2574</v>
+        <v>-0.5853</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6616</v>
+        <v>2.2697</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2281</v>
+        <v>2.7114</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4336</v>
+        <v>-0.4417</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0623</v>
+        <v>0.6092</v>
       </c>
       <c r="H4" t="n">
-        <v>1.083</v>
+        <v>-1.3159</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0208</v>
+        <v>1.9251</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.372</v>
+        <v>2.0029</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9424</v>
+        <v>-0.7097</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3144</v>
+        <v>2.7126</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4343</v>
+        <v>-1.3938</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1406</v>
+        <v>-0.6062</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2937</v>
+        <v>-0.7875</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7419</v>
+        <v>3.1336</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0079</v>
+        <v>-0.8913</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9502</v>
+        <v>-0.454</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9424</v>
+        <v>-0.4373</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8081</v>
+        <v>1.5726</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6083</v>
+        <v>3.3169</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1998</v>
+        <v>-1.7443</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2861</v>
+        <v>2.269</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2084</v>
+        <v>0.5763</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0777</v>
+        <v>1.6927</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1467</v>
+        <v>-0.2775</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0565</v>
+        <v>-0.5104</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2032</v>
+        <v>0.2328</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3998</v>
+        <v>0.6475</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5857</v>
+        <v>-0.2416</v>
       </c>
       <c r="L5" t="n">
-        <v>4.9855</v>
+        <v>0.8891</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2532</v>
+        <v>-0.925</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4708</v>
+        <v>-0.2687</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7823</v>
+        <v>-0.6563</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8421</v>
+        <v>0.1348</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0163</v>
+        <v>-0.0712</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1742</v>
+        <v>0.206</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5853</v>
+        <v>0.2574</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5853</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3589</v>
+        <v>1.6906</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2699</v>
+        <v>-0.9835</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6288</v>
+        <v>2.6741</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5623</v>
+        <v>0.0623</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3739</v>
+        <v>1.083</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1884</v>
+        <v>-1.0208</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0466</v>
+        <v>-0.372</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1021</v>
+        <v>0.9424</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.1487</v>
+        <v>-1.3144</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4843</v>
+        <v>0.4343</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.476</v>
+        <v>0.1406</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9603</v>
+        <v>0.2937</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9585</v>
+        <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0772</v>
+        <v>0.0369</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4399</v>
+        <v>0.7387</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3627</v>
+        <v>-0.7018</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0399</v>
+        <v>0.8081</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1767</v>
+        <v>0.1998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3217</v>
+        <v>1.5368</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8168</v>
+        <v>-1.0653</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4952</v>
+        <v>2.6021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6092</v>
+        <v>-1.5623</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3159</v>
+        <v>-0.3739</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9251</v>
+        <v>-1.1884</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0029</v>
+        <v>-2.0466</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7097</v>
+        <v>0.1021</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7126</v>
+        <v>-2.1487</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3938</v>
+        <v>0.4843</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6062</v>
+        <v>-0.476</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7875</v>
+        <v>0.9603</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1336</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8393</v>
+        <v>0.1007</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3486</v>
+        <v>-0.2353</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4907</v>
+        <v>0.336</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5726</v>
+        <v>1.0399</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3169</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7443</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.8289</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4735</v>
+        <v>-0.3547</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2871</v>
+        <v>-0.4742</v>
       </c>
       <c r="G8" t="n">
         <v>-0.08749999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>2.3502</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2371</v>
+        <v>-0.3054</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2088</v>
+        <v>-0.09</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0283</v>
+        <v>-0.2154</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6111</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3003</v>
+        <v>-3.0911</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0558</v>
+        <v>-0.9535</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2445</v>
+        <v>-2.1376</v>
       </c>
       <c r="G9" t="n">
         <v>0.2391</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2434</v>
+        <v>-0.0341</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7086</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.871</v>
+        <v>-4.3442</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2418</v>
+        <v>-4.8754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3707</v>
+        <v>0.5311</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9353</v>
@@ -1234,13 +1234,13 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8194</v>
+        <v>-0.2926</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4993</v>
+        <v>-0.1329</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3201</v>
+        <v>-0.1597</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9412</v>
@@ -1267,31 +1267,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.0268</v>
+        <v>7.917700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.648899999999999</v>
+        <v>3.539800000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>4.3778</v>
+        <v>4.3779</v>
       </c>
       <c r="G11" t="n">
         <v>1.2919</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0415</v>
+        <v>-2.041500000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3333</v>
+        <v>3.333300000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>6.187899999999999</v>
+        <v>6.187900000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.9895999999999998</v>
       </c>
       <c r="L11" t="n">
-        <v>5.198300000000001</v>
+        <v>5.1983</v>
       </c>
       <c r="M11" t="n">
         <v>-4.8961</v>
@@ -1312,16 +1312,16 @@
         <v>19.5849</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.9378</v>
+        <v>-2.0468</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4057</v>
+        <v>-0.5146999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-1.5321</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8387999999999998</v>
+        <v>0.8387999999999993</v>
       </c>
       <c r="W11" t="n">
         <v>9.617699999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.246</v>
+        <v>7.0437</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8501</v>
+        <v>6.0781</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3959</v>
+        <v>0.9656</v>
       </c>
       <c r="G12" t="n">
         <v>2.3762</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4358</v>
+        <v>0.362</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.485</v>
+        <v>-0.257</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0493</v>
+        <v>0.619</v>
       </c>
       <c r="V12" t="n">
         <v>4.5014</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0218</v>
+        <v>1.0274</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7846</v>
+        <v>0.7735</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2373</v>
+        <v>0.2539</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9926</v>
+        <v>2.3229</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5491</v>
+        <v>2.2521</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5417</v>
+        <v>0.0708</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2229</v>
+        <v>3.1854</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0612</v>
+        <v>2.4531</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1617</v>
+        <v>0.7323</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7697000000000001</v>
+        <v>-0.8625</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.201</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>-0.6615</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3502</v>
+        <v>-2.1543</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2043</v>
+        <v>0.4968</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9119</v>
+        <v>0.1906</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2925</v>
+        <v>0.3063</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6083</v>
+        <v>-0.8131</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.4481</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6083</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3821</v>
+        <v>0.3485</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6712</v>
+        <v>-1.0575</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2891</v>
+        <v>1.406</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3229</v>
+        <v>0.9926</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2521</v>
+        <v>-0.5491</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0708</v>
+        <v>1.5417</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1854</v>
+        <v>0.2229</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4531</v>
+        <v>0.0612</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7323</v>
+        <v>0.1617</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8625</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.201</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6615</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9792</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1543</v>
+        <v>-2.3502</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1485</v>
+        <v>1.5311</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0882</v>
+        <v>1.0698</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2367</v>
+        <v>0.4613</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8131</v>
+        <v>-0.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4481</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.365</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0858</v>
+        <v>0.2416</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6655</v>
+        <v>-0.5632</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7513</v>
+        <v>0.8048</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1633</v>
@@ -1624,13 +1624,13 @@
         <v>0.5875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3384</v>
+        <v>-0.1826</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0241</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3143</v>
+        <v>-0.2608</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6045</v>
+        <v>0.0574</v>
       </c>
       <c r="E16" t="n">
-        <v>1.566</v>
+        <v>1.7706</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1705</v>
+        <v>-1.7133</v>
       </c>
       <c r="G16" t="n">
         <v>1.6712</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.148</v>
+        <v>0.8099</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0929</v>
+        <v>0.2976</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0551</v>
+        <v>0.5123</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2486</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6818</v>
+        <v>-1.5868</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0189</v>
+        <v>-1.2236</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6629</v>
+        <v>-0.3632</v>
       </c>
       <c r="G17" t="n">
         <v>1.3799</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4095</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.504</v>
+        <v>0.2994</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0945</v>
+        <v>0.2051</v>
       </c>
       <c r="V17" t="n">
         <v>-2.1003</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.224</v>
+        <v>-1.9613</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1842</v>
+        <v>-2.0819</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0398</v>
+        <v>0.1206</v>
       </c>
       <c r="G18" t="n">
         <v>-4.1078</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2912</v>
+        <v>-0.0285</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2923</v>
+        <v>-0.19</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0011</v>
+        <v>0.1614</v>
       </c>
       <c r="V18" t="n">
         <v>0.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5468</v>
+        <v>-4.0317</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4544</v>
+        <v>-1.966</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0924</v>
+        <v>-2.0657</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7832</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9135</v>
+        <v>0.4286</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3213</v>
+        <v>0.348</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9145</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.7053</v>
+        <v>-6.1188</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.9266</v>
+        <v>-6.1079</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2213</v>
+        <v>-0.0109</v>
       </c>
       <c r="G20" t="n">
         <v>-4.9803</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4763</v>
+        <v>1.0628</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8557</v>
+        <v>-0.0371</v>
       </c>
       <c r="U20" t="n">
-        <v>1.332</v>
+        <v>1.0998</v>
       </c>
       <c r="V20" t="n">
         <v>0.7365</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0267</v>
+        <v>-4.98</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.377699999999999</v>
+        <v>-4.3779</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.648900000000001</v>
+        <v>-0.6022000000000004</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2918</v>
@@ -2092,13 +2092,13 @@
         <v>11.7508</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9377</v>
+        <v>4.9846</v>
       </c>
       <c r="T21" t="n">
         <v>1.5321</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4058</v>
+        <v>3.4524</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8385999999999986</v>
